--- a/artfynd/A 31339-2026 artfynd.xlsx
+++ b/artfynd/A 31339-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136156616</v>
       </c>
       <c r="B2" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31339-2026 artfynd.xlsx
+++ b/artfynd/A 31339-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136156616</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 31339-2026 artfynd.xlsx
+++ b/artfynd/A 31339-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136156616</v>
       </c>
       <c r="B2" t="n">
-        <v>92159</v>
+        <v>92164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136156615</v>
       </c>
       <c r="B3" t="n">
-        <v>78877</v>
+        <v>78879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136156611</v>
       </c>
       <c r="B4" t="n">
-        <v>80093</v>
+        <v>80095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136156610</v>
       </c>
       <c r="B5" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136156612</v>
       </c>
       <c r="B6" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
